--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261020.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261020.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>155,499</t>
+          <t>5,398,520</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,398,520</t>
+          <t>155,499</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>202611WTEX6F</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,020,822</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>202611WTEX6F</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1,020,822</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>954,659</t>
+          <t>3,370,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,370,000</t>
+          <t>954,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,335,384</t>
+          <t>7,306,249</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,306,249</t>
+          <t>1,335,384</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>2,232,107</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>2,232,107</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>326,000</t>
+          <t>296,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>296,000</t>
+          <t>326,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>773,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>773,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>338,000</t>
+          <t>174,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>423,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>174,000</t>
+          <t>338,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>423,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>693,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>693,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>73,000</t>
+          <t>259,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>259,000</t>
+          <t>73,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
